--- a/Sample Sizes By Step.xlsx
+++ b/Sample Sizes By Step.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jball\Documents\local-git\KRSP_exploring\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7646371-D0D6-49BE-A860-35FB332C0D54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58CCECCE-96BE-42C8-B402-5660A7E8DB2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{8DBE1842-90D7-491B-B4CD-F8D8B6831160}"/>
   </bookViews>
@@ -128,9 +128,6 @@
     <t>One squirrel on RR missing location</t>
   </si>
   <si>
-    <t>7: Final clean for anyone without location</t>
-  </si>
-  <si>
     <t>12030 were from census, 301 were from trapping</t>
   </si>
   <si>
@@ -333,6 +330,9 @@
   </si>
   <si>
     <t>7: How many are still missing location?</t>
+  </si>
+  <si>
+    <t>7: Remove anyone without location</t>
   </si>
 </sst>
 </file>
@@ -383,14 +383,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -741,12 +738,12 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.35">
@@ -771,7 +768,7 @@
         <v>54997</v>
       </c>
       <c r="D8" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.35">
@@ -784,7 +781,7 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B10">
         <v>12248</v>
@@ -806,7 +803,7 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C12">
         <v>310</v>
@@ -814,7 +811,7 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B13">
         <v>12248</v>
@@ -825,7 +822,7 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C14">
         <v>8</v>
@@ -844,18 +841,18 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
-        <v>29</v>
+        <v>97</v>
       </c>
       <c r="B16">
         <v>12331</v>
       </c>
       <c r="D16" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A19" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>0</v>
@@ -869,18 +866,18 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B20">
         <v>12331</v>
       </c>
       <c r="D20" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B21">
         <v>12331</v>
@@ -888,13 +885,13 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B22">
         <v>12331</v>
       </c>
       <c r="D22" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.35">
@@ -1013,7 +1010,7 @@
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A39" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>0</v>
@@ -1027,7 +1024,7 @@
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B40">
         <v>16395</v>
@@ -1035,7 +1032,7 @@
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B41">
         <v>8060</v>
@@ -1043,18 +1040,18 @@
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B42">
         <v>8060</v>
       </c>
       <c r="D42" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B43">
         <v>10850</v>
@@ -1062,7 +1059,7 @@
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C44">
         <v>2790</v>
@@ -1070,7 +1067,7 @@
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B45">
         <v>10850</v>
@@ -1079,12 +1076,12 @@
         <v>0</v>
       </c>
       <c r="D45" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A48" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>0</v>
@@ -1098,40 +1095,40 @@
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B49">
         <v>24040</v>
       </c>
       <c r="D49" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B50">
         <v>236</v>
       </c>
       <c r="D50" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C51">
         <v>124</v>
       </c>
       <c r="D51" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B52">
         <v>266</v>
@@ -1139,7 +1136,7 @@
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B53">
         <v>266</v>
@@ -1147,7 +1144,7 @@
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A56" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>0</v>
@@ -1161,18 +1158,18 @@
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B57">
         <v>2930</v>
       </c>
       <c r="D57" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B58">
         <v>2929</v>
@@ -1180,7 +1177,7 @@
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A61" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>0</v>
@@ -1193,178 +1190,172 @@
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A62" s="3" t="s">
-        <v>62</v>
+      <c r="A62" t="s">
+        <v>61</v>
       </c>
       <c r="B62">
         <v>2520</v>
       </c>
       <c r="D62" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A63" s="3" t="s">
-        <v>63</v>
+      <c r="A63" t="s">
+        <v>62</v>
       </c>
       <c r="B63">
         <v>2521</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A64" s="3" t="s">
-        <v>64</v>
+      <c r="A64" t="s">
+        <v>63</v>
       </c>
       <c r="C64">
         <v>117</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A65" s="3" t="s">
-        <v>65</v>
+      <c r="A65" t="s">
+        <v>64</v>
       </c>
       <c r="B65">
         <v>2521</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A66" s="3" t="s">
-        <v>66</v>
+      <c r="A66" t="s">
+        <v>65</v>
       </c>
       <c r="C66">
         <v>39</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A67" s="3" t="s">
-        <v>67</v>
+      <c r="A67" t="s">
+        <v>66</v>
       </c>
       <c r="B67">
         <v>2521</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A68" s="3" t="s">
-        <v>68</v>
+      <c r="A68" t="s">
+        <v>67</v>
       </c>
       <c r="C68">
         <v>0</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A69" s="3" t="s">
-        <v>69</v>
+      <c r="A69" t="s">
+        <v>68</v>
       </c>
       <c r="B69">
         <v>2521</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A70" s="3" t="s">
-        <v>70</v>
+      <c r="A70" t="s">
+        <v>69</v>
       </c>
       <c r="C70">
         <v>2010</v>
       </c>
       <c r="D70" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A71" t="s">
         <v>71</v>
-      </c>
-    </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A71" s="3" t="s">
-        <v>72</v>
       </c>
       <c r="B71">
         <v>2521</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A72" s="3" t="s">
-        <v>73</v>
+      <c r="A72" t="s">
+        <v>72</v>
       </c>
       <c r="C72">
         <v>25</v>
       </c>
       <c r="D72" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A73" t="s">
         <v>74</v>
-      </c>
-    </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A73" s="3" t="s">
-        <v>75</v>
       </c>
       <c r="B73">
         <v>2521</v>
       </c>
       <c r="D73" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A74" t="s">
         <v>76</v>
-      </c>
-    </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A74" s="3" t="s">
-        <v>77</v>
       </c>
       <c r="B74">
         <v>2521</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A75" s="3" t="s">
-        <v>78</v>
+      <c r="A75" t="s">
+        <v>77</v>
       </c>
       <c r="B75">
         <v>2521</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A76" s="3" t="s">
-        <v>79</v>
+      <c r="A76" t="s">
+        <v>78</v>
       </c>
       <c r="B76">
         <v>2519</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A77" s="3" t="s">
-        <v>80</v>
+      <c r="A77" t="s">
+        <v>79</v>
       </c>
       <c r="B77">
         <v>2463</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A78" s="3" t="s">
-        <v>81</v>
+      <c r="A78" t="s">
+        <v>80</v>
       </c>
       <c r="B78">
         <v>2292</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A79" s="3" t="s">
-        <v>82</v>
+      <c r="A79" t="s">
+        <v>81</v>
       </c>
       <c r="B79">
         <v>2133</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A80" s="3" t="s">
-        <v>83</v>
+      <c r="A80" t="s">
+        <v>82</v>
       </c>
       <c r="B80">
         <v>2133</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A81" s="3"/>
-    </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A82" s="3"/>
-    </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A83" s="6" t="s">
-        <v>92</v>
+      <c r="A83" s="1" t="s">
+        <v>91</v>
       </c>
       <c r="B83" s="1" t="s">
         <v>0</v>
@@ -1376,48 +1367,48 @@
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A84" s="4" t="s">
+    <row r="84" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A84" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="B84" s="3">
+        <v>457</v>
+      </c>
+      <c r="D84" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="B84" s="5">
-        <v>457</v>
-      </c>
-      <c r="D84" s="5" t="s">
+    </row>
+    <row r="85" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A85" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="B85" s="3">
+        <v>1211</v>
+      </c>
+      <c r="D85" s="3" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="85" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A85" s="4" t="s">
+    <row r="86" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A86" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="B85" s="5">
-        <v>1211</v>
-      </c>
-      <c r="D85" s="5" t="s">
+      <c r="B86" s="3">
+        <v>1988</v>
+      </c>
+      <c r="D86" s="3" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A87" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="B87" s="3">
+        <v>236</v>
+      </c>
+      <c r="D87" s="3" t="s">
         <v>86</v>
-      </c>
-    </row>
-    <row r="86" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A86" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="B86" s="5">
-        <v>1988</v>
-      </c>
-      <c r="D86" s="5" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="87" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A87" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="B87" s="5">
-        <v>236</v>
-      </c>
-      <c r="D87" s="5" t="s">
-        <v>87</v>
       </c>
     </row>
   </sheetData>

--- a/Sample Sizes By Step.xlsx
+++ b/Sample Sizes By Step.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jball\Documents\local-git\KRSP_exploring\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58CCECCE-96BE-42C8-B402-5660A7E8DB2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C611F6F8-9711-4195-8F54-927A6EF882FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{8DBE1842-90D7-491B-B4CD-F8D8B6831160}"/>
+    <workbookView xWindow="2436" yWindow="240" windowWidth="18660" windowHeight="11892" xr2:uid="{8DBE1842-90D7-491B-B4CD-F8D8B6831160}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -293,9 +293,6 @@
     <t>20. Make cache dataset</t>
   </si>
   <si>
-    <t>This is KL and SU, only including any litters with cache dat</t>
-  </si>
-  <si>
     <t>This is KL and SU for all years</t>
   </si>
   <si>
@@ -333,6 +330,9 @@
   </si>
   <si>
     <t>7: Remove anyone without location</t>
+  </si>
+  <si>
+    <t>This is KL and SU, only including litters with cache dat</t>
   </si>
 </sst>
 </file>
@@ -723,30 +723,30 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1CB4C470-D68A-4136-88E2-FAFCDBEE8177}">
   <dimension ref="A1:D87"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="62.1796875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.54296875" customWidth="1"/>
-    <col min="3" max="3" width="9.453125" customWidth="1"/>
-    <col min="4" max="4" width="38.36328125" customWidth="1"/>
+    <col min="1" max="1" width="62.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.5546875" customWidth="1"/>
+    <col min="3" max="3" width="9.44140625" customWidth="1"/>
+    <col min="4" max="4" width="38.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>27</v>
       </c>
@@ -760,7 +760,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>20</v>
       </c>
@@ -771,7 +771,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>21</v>
       </c>
@@ -779,7 +779,7 @@
         <v>39833</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>45</v>
       </c>
@@ -790,7 +790,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>23</v>
       </c>
@@ -801,17 +801,17 @@
         <v>24</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C12">
         <v>310</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B13">
         <v>12248</v>
@@ -820,15 +820,15 @@
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C14">
         <v>8</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>26</v>
       </c>
@@ -839,9 +839,9 @@
         <v>28</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B16">
         <v>12331</v>
@@ -850,7 +850,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
         <v>30</v>
       </c>
@@ -864,7 +864,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>31</v>
       </c>
@@ -875,7 +875,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>32</v>
       </c>
@@ -883,7 +883,7 @@
         <v>12331</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>35</v>
       </c>
@@ -894,7 +894,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
         <v>19</v>
       </c>
@@ -908,7 +908,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>4</v>
       </c>
@@ -919,7 +919,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>5</v>
       </c>
@@ -930,7 +930,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>6</v>
       </c>
@@ -938,7 +938,7 @@
         <v>16502</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>7</v>
       </c>
@@ -946,7 +946,7 @@
         <v>13410</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>8</v>
       </c>
@@ -954,7 +954,7 @@
         <v>8398</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>9</v>
       </c>
@@ -965,7 +965,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>10</v>
       </c>
@@ -973,7 +973,7 @@
         <v>7199</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>11</v>
       </c>
@@ -981,7 +981,7 @@
         <v>2520</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>13</v>
       </c>
@@ -989,7 +989,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>14</v>
       </c>
@@ -997,7 +997,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>15</v>
       </c>
@@ -1008,7 +1008,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
         <v>37</v>
       </c>
@@ -1022,7 +1022,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>46</v>
       </c>
@@ -1030,7 +1030,7 @@
         <v>16395</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>47</v>
       </c>
@@ -1038,7 +1038,7 @@
         <v>8060</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>48</v>
       </c>
@@ -1049,7 +1049,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>49</v>
       </c>
@@ -1057,7 +1057,7 @@
         <v>10850</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>50</v>
       </c>
@@ -1065,7 +1065,7 @@
         <v>2790</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>51</v>
       </c>
@@ -1079,7 +1079,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
         <v>40</v>
       </c>
@@ -1093,7 +1093,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>52</v>
       </c>
@@ -1104,7 +1104,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>54</v>
       </c>
@@ -1115,7 +1115,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>55</v>
       </c>
@@ -1126,7 +1126,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>57</v>
       </c>
@@ -1134,7 +1134,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>58</v>
       </c>
@@ -1142,7 +1142,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
         <v>56</v>
       </c>
@@ -1156,7 +1156,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>42</v>
       </c>
@@ -1167,7 +1167,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>43</v>
       </c>
@@ -1175,7 +1175,7 @@
         <v>2929</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A61" s="1" t="s">
         <v>59</v>
       </c>
@@ -1189,7 +1189,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>61</v>
       </c>
@@ -1200,7 +1200,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>62</v>
       </c>
@@ -1208,7 +1208,7 @@
         <v>2521</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>63</v>
       </c>
@@ -1216,7 +1216,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>64</v>
       </c>
@@ -1224,7 +1224,7 @@
         <v>2521</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>65</v>
       </c>
@@ -1232,7 +1232,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>66</v>
       </c>
@@ -1240,7 +1240,7 @@
         <v>2521</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>67</v>
       </c>
@@ -1248,7 +1248,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>68</v>
       </c>
@@ -1256,7 +1256,7 @@
         <v>2521</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>69</v>
       </c>
@@ -1267,7 +1267,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>71</v>
       </c>
@@ -1275,7 +1275,7 @@
         <v>2521</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>72</v>
       </c>
@@ -1286,7 +1286,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>74</v>
       </c>
@@ -1297,7 +1297,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>76</v>
       </c>
@@ -1305,7 +1305,7 @@
         <v>2521</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>77</v>
       </c>
@@ -1313,7 +1313,7 @@
         <v>2521</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>78</v>
       </c>
@@ -1321,7 +1321,7 @@
         <v>2519</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>79</v>
       </c>
@@ -1329,7 +1329,7 @@
         <v>2463</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>80</v>
       </c>
@@ -1337,7 +1337,7 @@
         <v>2292</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>81</v>
       </c>
@@ -1345,7 +1345,7 @@
         <v>2133</v>
       </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>82</v>
       </c>
@@ -1353,9 +1353,9 @@
         <v>2133</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A83" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B83" s="1" t="s">
         <v>0</v>
@@ -1367,7 +1367,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A84" s="3" t="s">
         <v>83</v>
       </c>
@@ -1375,40 +1375,40 @@
         <v>457</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="85" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.35">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A85" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B85" s="3">
         <v>1211</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="86" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.35">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A86" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B86" s="3">
         <v>1988</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="87" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.35">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A87" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B87" s="3">
         <v>236</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
   </sheetData>
